--- a/Tube_Thickness_Calculator.xlsx
+++ b/Tube_Thickness_Calculator.xlsx
@@ -27,13 +27,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="425">
   <si>
     <t xml:space="preserve">HEAT EXCHANGER
 TUBE THICKNESS CALCULATOR</t>
   </si>
   <si>
-    <t xml:space="preserve">Per ASME Sec VIII Div 1 | TEMA | API 660 | IOGP S-562</t>
+    <t xml:space="preserve">Per ASME Sec VIII Div 1 | TEMA | API 660 | IOGP S-614</t>
   </si>
   <si>
     <t xml:space="preserve">Standards Referenced</t>
@@ -60,10 +60,10 @@
     <t xml:space="preserve">Shell-and-tube HE requirements, tube sizing table</t>
   </si>
   <si>
-    <t xml:space="preserve">IOGP S-562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supplementary requirements for HE tube selection</t>
+    <t xml:space="preserve">IOGP S-614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplementary spec to API 660 for shell-and-tube HEs</t>
   </si>
   <si>
     <t xml:space="preserve">Color Legend</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">5. API_660 sheet checks minimum wall per API 660 Table 5.</t>
   </si>
   <si>
-    <t xml:space="preserve">6. IOGP sheet checks additional IOGP S-562 requirements.</t>
+    <t xml:space="preserve">6. IOGP sheet lists IOGP S-614 supplementary considerations (verify vs actual document).</t>
   </si>
   <si>
     <t xml:space="preserve">7. SUMMARY sheet shows governing (largest) required thickness and final PASS/FAIL.</t>
@@ -321,7 +321,7 @@
     <t xml:space="preserve">MPa</t>
   </si>
   <si>
-    <t xml:space="preserve">From MATERIALS sheet / ASME IID Table 1A</t>
+    <t xml:space="preserve">SA-179 example; see MATERIALS. VERIFY vs ASME II-D</t>
   </si>
   <si>
     <t xml:space="preserve">Young's Modulus at Design T</t>
@@ -459,7 +459,7 @@
     <t xml:space="preserve">MATERIALS — Allowable Stress (MPa) — Source: ASME Section IID Table 1A / 1B</t>
   </si>
   <si>
-    <t xml:space="preserve">Values from ASME BPVC IID (2021 Edition). Verify for project-specific edition.</t>
+    <t xml:space="preserve">Allowable stress S computed as min(UTS/3.5, 2*Yield/3) per ASME VIII-1 basis, room temp. INDICATIVE ONLY - verify EVERY value against ASME BPVC II-D Table 1A/1B for the controlling edition &amp; temperature before design use.</t>
   </si>
   <si>
     <t xml:space="preserve">Material</t>
@@ -504,22 +504,19 @@
     <t xml:space="preserve">SA-179 SMLS</t>
   </si>
   <si>
-    <t xml:space="preserve">CS seamless cold-drawn</t>
+    <t xml:space="preserve">S=UTS/3.5 (UTS 47ksi); flat &lt;=340C</t>
   </si>
   <si>
     <t xml:space="preserve">SA-192 SMLS</t>
   </si>
   <si>
-    <t xml:space="preserve">CS seamless for HEI</t>
-  </si>
-  <si>
     <t xml:space="preserve">C-Mo Steel</t>
   </si>
   <si>
     <t xml:space="preserve">SA-209 T1</t>
   </si>
   <si>
-    <t xml:space="preserve">1/2% Mo alloy</t>
+    <t xml:space="preserve">S=UTS/3.5 (UTS 55ksi); creep &gt;450C</t>
   </si>
   <si>
     <t xml:space="preserve">1-1/4Cr-1/2Mo</t>
@@ -528,7 +525,7 @@
     <t xml:space="preserve">SA-213 T11</t>
   </si>
   <si>
-    <t xml:space="preserve">Cr-Mo alloy</t>
+    <t xml:space="preserve">S=UTS/3.5 (UTS 60ksi); creep &gt;480C</t>
   </si>
   <si>
     <t xml:space="preserve">2-1/4Cr-1Mo</t>
@@ -543,13 +540,16 @@
     <t xml:space="preserve">SA-213 T5</t>
   </si>
   <si>
+    <t xml:space="preserve">S=UTS/3.5 (UTS 60ksi)</t>
+  </si>
+  <si>
     <t xml:space="preserve">9Cr-1Mo (P91)</t>
   </si>
   <si>
     <t xml:space="preserve">SA-213 T91</t>
   </si>
   <si>
-    <t xml:space="preserve">Modified 9Cr-1Mo</t>
+    <t xml:space="preserve">S=UTS/3.5 (UTS 85ksi)</t>
   </si>
   <si>
     <t xml:space="preserve">304 SS</t>
@@ -819,13 +819,13 @@
     <t xml:space="preserve">⚠  NOTE: External pressure calculation here uses an analytical approximation of ASME Figure G. For final design, the rigorous chart-based method per ASME VIII Div 1 UG-28 and Figure G + material charts (Section II Part D) MUST be followed. The approximation above is conservative for preliminary sizing only.</t>
   </si>
   <si>
-    <t xml:space="preserve">t_long = P_i·D_o / (4·S·E + 1.6·P_i)</t>
+    <t xml:space="preserve">t_long = P_i·D_o / (4·S·E − 0.8·P_i)  [Appendix 1-1(a)(2)]</t>
   </si>
   <si>
     <t xml:space="preserve">t_long</t>
   </si>
   <si>
-    <t xml:space="preserve">Longitudinal stress usually smaller than circumferential; shown for completeness</t>
+    <t xml:space="preserve">Longitudinal stress (circ. joints); ~half of circumferential, rarely governs</t>
   </si>
   <si>
     <t xml:space="preserve">Governing ASME thickness (max of int. and long.)</t>
@@ -837,13 +837,52 @@
     <t xml:space="preserve">Governs for thickness ordering (before CA &amp; MT)</t>
   </si>
   <si>
-    <t xml:space="preserve">TEMA — MINIMUM TUBE WALL THICKNESS (10th Edition)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference: TEMA RGP-T-2.4 Table — Minimum Tube Wall Thickness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEMA RGP-T-2.4: Minimum Required Wall Thickness vs Tube OD</t>
+    <t xml:space="preserve">FORMULA VALIDATION — against published UG-27 worked example</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validation Step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example inputs (Kezar Eng.): P=1.60 MPa, R_i=1000 mm, S=138 MPa, E=0.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Published circumferential answer = 13.75 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID form t = P·R/(S·E − 0.6·P)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t_ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Should reproduce 13.75 mm → validates ID formula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OD form (this sheet's method), D_o = 2020 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t_OD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same case via OD form used by this workbook (~13.70 mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agreement within ID/OD rounding (&lt;0.5%)?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirms the sheet's OD formula matches the published result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEMA — MINIMUM TUBE WALL (gauge) GUIDANCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commonly specified minimum tube gauges (industry practice). VERIFY against TEMA tube tables (Table D-7 / RCB-2.4) for your class R / C / B.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common Minimum Tube Gauge vs Tube OD (nominal/ordered wall)</t>
   </si>
   <si>
     <t xml:space="preserve">Tube OD (in)</t>
@@ -897,7 +936,7 @@
     <t xml:space="preserve">t_min_avail</t>
   </si>
   <si>
-    <t xml:space="preserve">TEMA MINIMUM WALL CHECK: t_nom×(1–MT) ≥ t_TEMA?</t>
+    <t xml:space="preserve">GAUGE CHECK: ordered wall t_nom ≥ min gauge?  (net-wall adequacy is covered by ASME_VIII)</t>
   </si>
   <si>
     <t xml:space="preserve">BWG REFERENCE TABLE (Wall Thickness in mm)</t>
@@ -909,52 +948,55 @@
     <t xml:space="preserve">Wall (mm)</t>
   </si>
   <si>
-    <t xml:space="preserve">API 660 9th EDITION — TUBE THICKNESS REQUIREMENTS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference: API 660 Table 5 — Minimum Tube Wall Thickness; Clause 5.2.3 / 5.3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">API 660 TABLE 5: Minimum Tube Wall Thickness (purchased condition)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS / Low-Alloy Min Wall (mm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stainless / Ni-Alloy Min Wall (mm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Ferrous Min Wall (mm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5/8" OD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/4" OD — most common size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7/8" OD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1" OD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-1/4" OD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-1/2" OD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2" OD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-1/2" OD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3" OD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clause</t>
+    <t xml:space="preserve">API 660 9th EDITION (2015) — TUBE THICKNESS REQUIREMENTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference: API 660 Table 1 'Minimum Thickness of Tubes'. It is a minimum ORDERED (nominal) wall floor BY MATERIAL CLASS — it does NOT vary with tube OD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API 660 TABLE 1: Minimum Thickness of Tubes (by material class)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material Class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min Wall (in)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≈ BWG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carbon steel, low-alloy steel (&lt;=9% Cr), aluminium &amp; Al alloys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 BWG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Most common class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copper alloys &amp; high-alloy (stainless) steels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~17 BWG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8th Ed: Cu alloys = 1.65 mm (0.065")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titanium &amp; titanium alloys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~19 BWG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thinnest permitted class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1 is a FLOOR only: tube wall shall be the greater of this value, the ASME VIII pressure-design thickness, and any purchaser-specified corrosion/bend-thinning allowance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Topic</t>
   </si>
   <si>
     <t xml:space="preserve">Requirement</t>
@@ -963,205 +1005,175 @@
     <t xml:space="preserve">Complied?</t>
   </si>
   <si>
-    <t xml:space="preserve">Cl. 5.2.3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tubes shall be seamless if available in the material grade</t>
+    <t xml:space="preserve">Tubes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tubes shall be seamless unless welded tube is specified / agreed</t>
   </si>
   <si>
     <t xml:space="preserve">Yes / To be confirmed</t>
   </si>
   <si>
-    <t xml:space="preserve">Cl. 5.2.3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tube shall conform to ASME VIII UG-31; thickness per UG-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl. 5.2.3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minimum wall after mill tolerance ≥ values in Table 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl. 5.2.3.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corroded wall thickness shall meet pressure design requirements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl. 5.3.3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mill tolerance: 12.5% for carbon/alloy steel per ASTM; verify per material spec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl. 5.3.3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tubes for H₂S service per NACE MR0175/ISO 15156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl. 5.3.3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tube-to-tubesheet joint: specify strength-welded or expanded; seal-welded in corrosive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl. 5.3.3.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bi-metallic tubes or tubes with cladding: minimum net wall of base material applies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl. 6.1.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hydrotest: ASME VIII UG-99 or UG-100 as applicable; pneumatic requires additional NDE</t>
+    <t xml:space="preserve">Thickness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wall &gt;= API 660 Table 1 min AND &gt;= ASME VIII pressure-design thickness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrosion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add any purchaser-specified tube corrosion allowance on top of Table 1 floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U-bends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U-bend wall after thinning &gt;= pressure-code min + corrosion allowance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mill tol.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account for wall undertolerance (e.g. 12.5% for many ASTM tube specs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sour svc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H2S service: tubes per NACE MR0175 / ISO 15156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tube-to-tubesheet joint (expanded / strength-welded) per service &amp; TEMA class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydrostatic / NDE per ASME VIII and TEMA class as specified</t>
   </si>
   <si>
     <t xml:space="preserve">API 660 WALL THICKNESS COMPLIANCE CHECK</t>
   </si>
   <si>
-    <t xml:space="preserve">Material Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">API 660 Min wall (CS/Low-Alloy) for this OD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t_API_CS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">API 660 Min wall (SS/Ni-Alloy) for this OD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t_API_SS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t_min_a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">API 660 WALL CHECK (CS/Low-Alloy): t_min_a ≥ t_API_CS?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOGP S-562 — SUPPLEMENTARY REQUIREMENTS FOR SHELL-AND-TUBE HEs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference: IOGP S-562 (formerly IOGP GP 24-01, superseded from SP-1198); based on 2022 edition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOGP S-562 KEY TUBE REQUIREMENTS</t>
+    <t xml:space="preserve">Nominal (ordered) wall (from INPUTS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tube material (from INPUTS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API 660 min — CS/low-alloy/Al class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t_API_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API 660 min — Cu-alloy/stainless class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t_API_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API 660 min — Titanium class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t_API_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API 660 CHECK (CS/low-alloy class): ordered wall t_nom ≥ 2.11 mm (Table 1)?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For Cu/stainless use row 33 (1.47); for Ti use row 34 (1.07)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IOGP S-614 — SUPPLEMENTARY SPEC TO API 660 (SHELL &amp; TUBE HEAT EXCHANGERS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IOGP S-614 supplements API 660. It requires the minimum tube wall and bend-thinning allowance to be STATED IN THE PURCHASE DOCUMENTS. Items below are TYPICAL considerations - verify against the actual S-614 text &amp; project data sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IOGP S-614 / PROJECT TUBE CONSIDERATIONS (paraphrased)</t>
   </si>
   <si>
     <t xml:space="preserve">Status</t>
   </si>
   <si>
-    <t xml:space="preserve">S-562 §6.2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tubes shall be seamless for all pressure-containing services</t>
+    <t xml:space="preserve">Tube wall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum required tube wall thickness shall be stated in the purchase documents (S-614)</t>
   </si>
   <si>
     <t xml:space="preserve">Yes / N/A</t>
   </si>
   <si>
-    <t xml:space="preserve">S-562 §6.2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minimum nominal wall thickness: 1.651 mm (16 BWG) for tube OD ≤ 19.05 mm; 2.108 mm (14 BWG) for OD 19.05–25.4 mm; 2.769 mm (12 BWG) for OD &gt; 25.4 mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-562 §6.2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For H₂S-containing service: tubes per NACE MR0175/ISO 15156-2/-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-562 §6.2.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrosion allowance: minimum 0.5 mm on shell-side if carbon steel shell; tube-side per process corrosion analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-562 §6.2.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tube-to-tubesheet joint: strength-welded + full-depth expansion for lethal service; strength-welded + partial expansion for general service; expanded only NOT permitted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-562 §6.2.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tubes in cooling water service: min. 1.651 mm (16 BWG) regardless of material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-562 §6.2.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tube surface finish: Ra ≤ 3.2 µm on shell side for fouling service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-562 §6.3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mill test certificates required: dual-certified (chemical + mechanical) per ASME IID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-562 §6.3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDE: 100% eddy-current testing of all austenitic SS, Ni-alloy and non-ferrous tubes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-562 §6.3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All CS/LAS tubes: 100% hydrostatic pressure test or eddy-current (per TEMA class)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-562 §6.4.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design temperature: include solar radiation if exposed; add 15°C if outdoors (hot climate)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-562 §6.4.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upset conditions: tubes designed for 110% of normal operating pressure and temperature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-562 §7.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Documentation: tube dimension drawing, material certs, test records, inspection release</t>
+    <t xml:space="preserve">Bend thinning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bend-thinning allowance for U-tubes, when applicable, stated in purchase documents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base codes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplements API 660 - API 660 Table 1 floor AND ASME VIII pressure design still apply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seamless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seamless tubes generally required for pressure service unless agreed otherwise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sour service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplementary NDE (e.g. 100% eddy-current) per project specification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material certs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mill / material test certificates per EN 10204 3.1/3.2 or ASME as specified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All project-specific tube requirements captured on the API 660 / IOGP data sheet</t>
   </si>
   <si>
     <t xml:space="preserve">IOGP MINIMUM WALL THICKNESS CHECK</t>
   </si>
   <si>
-    <t xml:space="preserve">Nominal wall (from INPUTS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOGP S-562 §6.2.2 min wall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t_IOGP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Min. net wall = t_nom×(1–MT)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t_net</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOGP min. net wall after CA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t_net_ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOGP WALL CHECK: t_nom ≥ t_IOGP (§6.2.2)?</t>
+    <t xml:space="preserve">API 660 Table 1 floor (CS/low-alloy class)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t_API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project-specified min wall (purchase doc)  &lt;-- EDIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t_spec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Governing IOGP min = MAX(API floor, project)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t_gov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IOGP CHECK: ordered wall t_nom ≥ governing min (API floor + project spec)?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yellow cell D25 = project value from purchase docs</t>
   </si>
   <si>
     <t xml:space="preserve">TUBE THICKNESS CALCULATION SUMMARY</t>
@@ -1224,22 +1236,22 @@
     <t xml:space="preserve">UG-31</t>
   </si>
   <si>
-    <t xml:space="preserve">TEMA RGP-T-2.4 Minimum Wall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RGP-T-2.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">API 660 Table 5 Min Wall (CS/Low-Alloy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">API660 T5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOGP S-562 §6.2.2 Min Wall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S-562</t>
+    <t xml:space="preserve">TEMA min tube gauge (common practice)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API 660 Table 1 min (CS/low-alloy class)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API660 T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IOGP S-614 governing min wall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-614</t>
   </si>
   <si>
     <t xml:space="preserve">GOVERNING REQUIRED THICKNESS (MAX of all standards)</t>
@@ -1290,7 +1302,7 @@
     <t xml:space="preserve">A_HT</t>
   </si>
   <si>
-    <t xml:space="preserve">DISCLAIMER: This spreadsheet is a calculation aid. Results shall be verified by a qualified engineer against the applicable edition of ASME VIII, TEMA, API 660 and IOGP S-562. The engineer of record is responsible for all design decisions.</t>
+    <t xml:space="preserve">DISCLAIMER: This spreadsheet is a calculation aid. Results shall be verified by a qualified engineer against the applicable edition of ASME VIII, TEMA, API 660 and IOGP S-614. The engineer of record is responsible for all design decisions.</t>
   </si>
 </sst>
 </file>
@@ -1304,8 +1316,8 @@
     <numFmt numFmtId="167" formatCode="0.0#"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
-    <numFmt numFmtId="170" formatCode="0.000&quot; in&quot;"/>
-    <numFmt numFmtId="171" formatCode="@"/>
+    <numFmt numFmtId="170" formatCode="@"/>
+    <numFmt numFmtId="171" formatCode="0.000&quot; in&quot;"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -1479,7 +1491,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1525,7 +1537,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
-        <bgColor rgb="FFDEEAF1"/>
+        <bgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -1544,6 +1556,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF9DC3E6"/>
         <bgColor rgb="FFC0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -1609,7 +1627,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="83">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1794,7 +1812,15 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1810,7 +1836,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1834,6 +1860,14 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="16" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1854,7 +1888,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1864,6 +1902,10 @@
     </xf>
     <xf numFmtId="164" fontId="19" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -2054,8 +2096,8 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFE2EFDA"/>
+      <rgbColor rgb="FFE2F0D9"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF9DC3E6"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -2823,7 +2865,7 @@
         <v>95</v>
       </c>
       <c r="D31" s="28" t="n">
-        <v>137.9</v>
+        <v>92.6</v>
       </c>
       <c r="E31" s="21" t="s">
         <v>96</v>
@@ -3167,7 +3209,7 @@
       <c r="L1" s="18"/>
       <c r="M1" s="18"/>
     </row>
-    <row r="2" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="30" t="s">
         <v>143</v>
       </c>
@@ -3232,34 +3274,34 @@
         <v>325</v>
       </c>
       <c r="E4" s="34" t="n">
-        <v>137.9</v>
+        <v>92.6</v>
       </c>
       <c r="F4" s="34" t="n">
-        <v>137.9</v>
+        <v>92.6</v>
       </c>
       <c r="G4" s="34" t="n">
-        <v>137.9</v>
+        <v>92.6</v>
       </c>
       <c r="H4" s="34" t="n">
-        <v>137.9</v>
+        <v>92.6</v>
       </c>
       <c r="I4" s="34" t="n">
-        <v>137.9</v>
+        <v>92.6</v>
       </c>
       <c r="J4" s="34" t="n">
-        <v>137.9</v>
+        <v>92.6</v>
       </c>
       <c r="K4" s="34" t="n">
-        <v>121.4</v>
+        <v>92.6</v>
       </c>
       <c r="L4" s="34" t="n">
-        <v>108.3</v>
+        <v>92.6</v>
       </c>
       <c r="M4" s="34" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="35" t="s">
         <v>156</v>
       </c>
@@ -3270,183 +3312,183 @@
         <v>325</v>
       </c>
       <c r="E5" s="36" t="n">
-        <v>137.9</v>
+        <v>92.6</v>
       </c>
       <c r="F5" s="36" t="n">
-        <v>137.9</v>
+        <v>92.6</v>
       </c>
       <c r="G5" s="36" t="n">
-        <v>137.9</v>
+        <v>92.6</v>
       </c>
       <c r="H5" s="36" t="n">
-        <v>137.9</v>
+        <v>92.6</v>
       </c>
       <c r="I5" s="36" t="n">
-        <v>137.9</v>
+        <v>92.6</v>
       </c>
       <c r="J5" s="36" t="n">
-        <v>137.9</v>
+        <v>92.6</v>
       </c>
       <c r="K5" s="36" t="n">
-        <v>121.4</v>
+        <v>92.6</v>
       </c>
       <c r="L5" s="36" t="n">
-        <v>108.3</v>
+        <v>92.6</v>
       </c>
       <c r="M5" s="36" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="33" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="33" t="s">
+      <c r="C6" s="33" t="s">
         <v>161</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>162</v>
       </c>
       <c r="D6" s="33" t="n">
         <v>380</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>165.5</v>
+        <v>108.6</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>165.5</v>
+        <v>108.6</v>
       </c>
       <c r="G6" s="34" t="n">
-        <v>165.5</v>
+        <v>108.6</v>
       </c>
       <c r="H6" s="34" t="n">
-        <v>165.5</v>
+        <v>108.6</v>
       </c>
       <c r="I6" s="34" t="n">
-        <v>165.5</v>
+        <v>108.6</v>
       </c>
       <c r="J6" s="34" t="n">
-        <v>165.5</v>
+        <v>108.6</v>
       </c>
       <c r="K6" s="34" t="n">
-        <v>158.6</v>
+        <v>108.6</v>
       </c>
       <c r="L6" s="34" t="n">
-        <v>151.7</v>
+        <v>105</v>
       </c>
       <c r="M6" s="34" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="35" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="35" t="s">
+      <c r="C7" s="35" t="s">
         <v>164</v>
-      </c>
-      <c r="C7" s="35" t="s">
-        <v>165</v>
       </c>
       <c r="D7" s="35" t="n">
         <v>415</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>175.8</v>
+        <v>118.6</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>175.8</v>
+        <v>118.6</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>175.8</v>
+        <v>118.6</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>175.8</v>
+        <v>118.6</v>
       </c>
       <c r="I7" s="36" t="n">
-        <v>175.8</v>
+        <v>118.6</v>
       </c>
       <c r="J7" s="36" t="n">
-        <v>175.8</v>
+        <v>118.6</v>
       </c>
       <c r="K7" s="36" t="n">
-        <v>175.8</v>
+        <v>118.6</v>
       </c>
       <c r="L7" s="36" t="n">
-        <v>175.8</v>
+        <v>118.6</v>
       </c>
       <c r="M7" s="36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="33" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="33" t="s">
+      <c r="C8" s="33" t="s">
         <v>167</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>168</v>
       </c>
       <c r="D8" s="33" t="n">
         <v>415</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>175.8</v>
+        <v>118.6</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>175.8</v>
+        <v>118.6</v>
       </c>
       <c r="G8" s="34" t="n">
-        <v>175.8</v>
+        <v>118.6</v>
       </c>
       <c r="H8" s="34" t="n">
-        <v>175.8</v>
+        <v>118.6</v>
       </c>
       <c r="I8" s="34" t="n">
-        <v>175.8</v>
+        <v>118.6</v>
       </c>
       <c r="J8" s="34" t="n">
-        <v>175.8</v>
+        <v>118.6</v>
       </c>
       <c r="K8" s="34" t="n">
-        <v>175.8</v>
+        <v>118.6</v>
       </c>
       <c r="L8" s="34" t="n">
-        <v>175.8</v>
+        <v>118.6</v>
       </c>
       <c r="M8" s="34" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="35" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="35" t="s">
         <v>169</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>170</v>
       </c>
       <c r="D9" s="35" t="n">
         <v>415</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>138</v>
+        <v>118.6</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>138</v>
+        <v>118.6</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>138</v>
+        <v>118.6</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>138</v>
+        <v>118.6</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>138</v>
+        <v>118.6</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>138</v>
+        <v>118.6</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>138</v>
+        <v>118.6</v>
       </c>
       <c r="L9" s="36" t="n">
-        <v>138</v>
+        <v>118.6</v>
       </c>
       <c r="M9" s="36" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3460,28 +3502,28 @@
         <v>585</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>198.6</v>
+        <v>167.1</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>198.6</v>
+        <v>167.1</v>
       </c>
       <c r="G10" s="34" t="n">
-        <v>198.6</v>
+        <v>167.1</v>
       </c>
       <c r="H10" s="34" t="n">
-        <v>198.6</v>
+        <v>167.1</v>
       </c>
       <c r="I10" s="34" t="n">
-        <v>198.6</v>
+        <v>167.1</v>
       </c>
       <c r="J10" s="34" t="n">
-        <v>198.6</v>
+        <v>167.1</v>
       </c>
       <c r="K10" s="34" t="n">
-        <v>198.6</v>
+        <v>167.1</v>
       </c>
       <c r="L10" s="34" t="n">
-        <v>198.6</v>
+        <v>167.1</v>
       </c>
       <c r="M10" s="34" t="s">
         <v>173</v>
@@ -3980,7 +4022,7 @@
     <tabColor rgb="FF2E75B6"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:F41"/>
+  <dimension ref="B1:F48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -4091,7 +4133,7 @@
       </c>
       <c r="D9" s="39" t="n">
         <f aca="false">INPUTS!D31</f>
-        <v>137.9</v>
+        <v>92.6</v>
       </c>
       <c r="E9" s="21" t="s">
         <v>96</v>
@@ -4211,7 +4253,7 @@
       </c>
       <c r="D18" s="41" t="n">
         <f aca="false">D7*D5/(2*(D9*D10+0.4*D7))</f>
-        <v>0.273118279569893</v>
+        <v>0.404458598726115</v>
       </c>
       <c r="E18" s="21" t="s">
         <v>53</v>
@@ -4229,7 +4271,7 @@
       </c>
       <c r="D19" s="41" t="n">
         <f aca="false">(D18+D11)/(1-D12)</f>
-        <v>1.45499231950845</v>
+        <v>1.60509554140127</v>
       </c>
       <c r="E19" s="21" t="s">
         <v>53</v>
@@ -4265,7 +4307,7 @@
       </c>
       <c r="D21" s="41" t="n">
         <f aca="false">2*D9*D10*D20/(D5-0.8*D20)</f>
-        <v>12.7031921841833</v>
+        <v>8.53020736950961</v>
       </c>
       <c r="E21" s="21" t="s">
         <v>96</v>
@@ -4283,7 +4325,7 @@
       </c>
       <c r="D22" s="41" t="n">
         <f aca="false">D21/0.1</f>
-        <v>127.031921841833</v>
+        <v>85.3020736950961</v>
       </c>
       <c r="E22" s="21" t="s">
         <v>74</v>
@@ -4415,7 +4457,7 @@
       </c>
       <c r="D31" s="39" t="n">
         <f aca="false">D9*D20/(0.5*D5)</f>
-        <v>12.2517454068241</v>
+        <v>8.22706036745407</v>
       </c>
       <c r="E31" s="21" t="s">
         <v>96</v>
@@ -4433,7 +4475,7 @@
       </c>
       <c r="D32" s="39" t="n">
         <f aca="false">MIN(D30,D31)</f>
-        <v>12.2517454068241</v>
+        <v>8.22706036745407</v>
       </c>
       <c r="E32" s="21" t="s">
         <v>96</v>
@@ -4453,7 +4495,7 @@
       </c>
       <c r="E33" s="33" t="str">
         <f aca="false">_xlfn.CONCAT("P_a=",TEXT(D32,"0.000")," MPa  vs  P_e=",TEXT(D8,"0.000")," MPa")</f>
-        <v>P_a=12.252 MPa  vs  P_e=0.010 MPa</v>
+        <v>P_a=8.227 MPa  vs  P_e=0.010 MPa</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4489,8 +4531,8 @@
         <v>264</v>
       </c>
       <c r="D38" s="41" t="n">
-        <f aca="false">D7*D5/(4*D9*D10+1.6*D7)</f>
-        <v>0.136559139784946</v>
+        <f aca="false">D7*D5/(4*D9*D10-0.8*D7)</f>
+        <v>0.207516339869281</v>
       </c>
       <c r="E38" s="21" t="s">
         <v>53</v>
@@ -4508,7 +4550,7 @@
       </c>
       <c r="D39" s="41" t="n">
         <f aca="false">MAX(D18,D38)</f>
-        <v>0.273118279569893</v>
+        <v>0.404458598726115</v>
       </c>
       <c r="E39" s="21" t="s">
         <v>53</v>
@@ -4519,6 +4561,100 @@
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+    </row>
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D43" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="E43" s="23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="40" t="s">
+        <v>271</v>
+      </c>
+      <c r="C44" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="D44" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="E44" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B45" s="40" t="s">
+        <v>273</v>
+      </c>
+      <c r="C45" s="38" t="s">
+        <v>274</v>
+      </c>
+      <c r="D45" s="47" t="n">
+        <f aca="false">1.6*1000/(138*0.85-0.6*1.6)</f>
+        <v>13.752793536187</v>
+      </c>
+      <c r="E45" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="40" t="s">
+        <v>276</v>
+      </c>
+      <c r="C46" s="38" t="s">
+        <v>277</v>
+      </c>
+      <c r="D46" s="47" t="n">
+        <f aca="false">1.6*2020/(2*(138*0.85+0.4*1.6))</f>
+        <v>13.7018823130405</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B47" s="40" t="s">
+        <v>279</v>
+      </c>
+      <c r="C47" s="38" t="s">
+        <v>280</v>
+      </c>
+      <c r="D47" s="46" t="str">
+        <f aca="false">IF(ABS(D45-D46)/D45&lt;0.01,"VALIDATED","REVIEW")</f>
+        <v>VALIDATED</v>
+      </c>
+      <c r="E47" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B1:E1"/>
@@ -4540,6 +4676,11 @@
     </cfRule>
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>D33="FAIL"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D47">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>D47="VALIDATED"</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4572,7 +4713,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="18" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
@@ -4580,7 +4721,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="30" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
@@ -4589,7 +4730,7 @@
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="19" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="20"/>
@@ -4599,196 +4740,196 @@
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="23" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="F5" s="23" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="46" t="n">
+      <c r="B6" s="48" t="n">
         <v>0.5</v>
       </c>
-      <c r="C6" s="47" t="n">
+      <c r="C6" s="49" t="n">
         <v>12.7</v>
       </c>
-      <c r="D6" s="48" t="n">
+      <c r="D6" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="E6" s="47" t="n">
+      <c r="E6" s="49" t="n">
         <v>1.245</v>
       </c>
-      <c r="F6" s="49" t="s">
-        <v>276</v>
+      <c r="F6" s="51" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="50" t="n">
+      <c r="B7" s="52" t="n">
         <v>0.625</v>
       </c>
-      <c r="C7" s="51" t="n">
+      <c r="C7" s="53" t="n">
         <v>15.875</v>
       </c>
-      <c r="D7" s="52" t="n">
+      <c r="D7" s="54" t="n">
         <v>18</v>
       </c>
-      <c r="E7" s="51" t="n">
+      <c r="E7" s="53" t="n">
         <v>1.245</v>
       </c>
-      <c r="F7" s="53" t="s">
-        <v>277</v>
+      <c r="F7" s="55" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="46" t="n">
+      <c r="B8" s="48" t="n">
         <v>0.75</v>
       </c>
-      <c r="C8" s="47" t="n">
+      <c r="C8" s="49" t="n">
         <v>19.05</v>
       </c>
-      <c r="D8" s="48" t="n">
+      <c r="D8" s="50" t="n">
         <v>16</v>
       </c>
-      <c r="E8" s="47" t="n">
+      <c r="E8" s="49" t="n">
         <v>1.651</v>
       </c>
-      <c r="F8" s="49" t="s">
-        <v>278</v>
+      <c r="F8" s="51" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="50" t="n">
+      <c r="B9" s="52" t="n">
         <v>0.875</v>
       </c>
-      <c r="C9" s="51" t="n">
+      <c r="C9" s="53" t="n">
         <v>22.225</v>
       </c>
-      <c r="D9" s="52" t="n">
+      <c r="D9" s="54" t="n">
         <v>16</v>
       </c>
-      <c r="E9" s="51" t="n">
+      <c r="E9" s="53" t="n">
         <v>1.651</v>
       </c>
-      <c r="F9" s="53" t="s">
-        <v>279</v>
+      <c r="F9" s="55" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="46" t="n">
+      <c r="B10" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="47" t="n">
+      <c r="C10" s="49" t="n">
         <v>25.4</v>
       </c>
-      <c r="D10" s="48" t="n">
+      <c r="D10" s="50" t="n">
         <v>14</v>
       </c>
-      <c r="E10" s="47" t="n">
+      <c r="E10" s="49" t="n">
         <v>2.108</v>
       </c>
-      <c r="F10" s="49" t="s">
-        <v>280</v>
+      <c r="F10" s="51" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="50" t="n">
+      <c r="B11" s="52" t="n">
         <v>1.25</v>
       </c>
-      <c r="C11" s="51" t="n">
+      <c r="C11" s="53" t="n">
         <v>31.75</v>
       </c>
-      <c r="D11" s="52" t="n">
+      <c r="D11" s="54" t="n">
         <v>14</v>
       </c>
-      <c r="E11" s="51" t="n">
+      <c r="E11" s="53" t="n">
         <v>2.108</v>
       </c>
-      <c r="F11" s="53" t="s">
-        <v>281</v>
+      <c r="F11" s="55" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="46" t="n">
+      <c r="B12" s="48" t="n">
         <v>1.5</v>
       </c>
-      <c r="C12" s="47" t="n">
+      <c r="C12" s="49" t="n">
         <v>38.1</v>
       </c>
-      <c r="D12" s="48" t="n">
+      <c r="D12" s="50" t="n">
         <v>12</v>
       </c>
-      <c r="E12" s="47" t="n">
+      <c r="E12" s="49" t="n">
         <v>2.769</v>
       </c>
-      <c r="F12" s="49" t="s">
-        <v>279</v>
+      <c r="F12" s="51" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="50" t="n">
+      <c r="B13" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="51" t="n">
+      <c r="C13" s="53" t="n">
         <v>50.8</v>
       </c>
-      <c r="D13" s="52" t="n">
+      <c r="D13" s="54" t="n">
         <v>12</v>
       </c>
-      <c r="E13" s="51" t="n">
+      <c r="E13" s="53" t="n">
         <v>2.769</v>
       </c>
-      <c r="F13" s="53" t="s">
-        <v>279</v>
+      <c r="F13" s="55" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="46" t="n">
+      <c r="B14" s="48" t="n">
         <v>2.5</v>
       </c>
-      <c r="C14" s="47" t="n">
+      <c r="C14" s="49" t="n">
         <v>63.5</v>
       </c>
-      <c r="D14" s="48" t="n">
+      <c r="D14" s="50" t="n">
         <v>10</v>
       </c>
-      <c r="E14" s="47" t="n">
+      <c r="E14" s="49" t="n">
         <v>3.404</v>
       </c>
-      <c r="F14" s="49" t="s">
-        <v>279</v>
+      <c r="F14" s="51" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="50" t="n">
+      <c r="B15" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="51" t="n">
+      <c r="C15" s="53" t="n">
         <v>76.2</v>
       </c>
-      <c r="D15" s="52" t="n">
+      <c r="D15" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="E15" s="51" t="n">
+      <c r="E15" s="53" t="n">
         <v>3.404</v>
       </c>
-      <c r="F15" s="53" t="s">
-        <v>279</v>
+      <c r="F15" s="55" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="19" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="20"/>
@@ -4810,7 +4951,7 @@
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="21" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="C20" s="38" t="s">
         <v>52</v>
@@ -4825,7 +4966,7 @@
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="21" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="C21" s="38" t="s">
         <v>56</v>
@@ -4840,10 +4981,10 @@
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="21" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="D22" s="41" t="n">
         <f aca="false">IFERROR(INDEX(E6:E15,MATCH(D20,C6:C15,0)),"OD not in TEMA table")</f>
@@ -4855,10 +4996,10 @@
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="21" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="D23" s="41" t="n">
         <f aca="false">INPUTS!D14*(1-INPUTS!D39/100)</f>
@@ -4870,11 +5011,11 @@
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="42" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="C24" s="42"/>
       <c r="D24" s="43" t="str">
-        <f aca="false">IF(ISNUMBER(D22),IF(D23&gt;=D22,"PASS","FAIL"),"N/A - check OD")</f>
+        <f aca="false">IF(ISNUMBER(D22),IF(D21&gt;=D22,"PASS","FAIL"),"N/A - check OD")</f>
         <v>PASS</v>
       </c>
       <c r="E24" s="44"/>
@@ -4882,7 +5023,7 @@
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="19" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="20"/>
@@ -4891,41 +5032,41 @@
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="23" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="C28" s="54" t="n">
+      <c r="C28" s="56" t="n">
         <v>4.572</v>
       </c>
       <c r="D28" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="E28" s="54" t="n">
+      <c r="E28" s="56" t="n">
         <v>4.191</v>
       </c>
       <c r="F28" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="G28" s="54" t="n">
+      <c r="G28" s="56" t="n">
         <v>3.759</v>
       </c>
     </row>
@@ -4933,19 +5074,19 @@
       <c r="B29" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="C29" s="55" t="n">
+      <c r="C29" s="57" t="n">
         <v>3.404</v>
       </c>
       <c r="D29" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="E29" s="55" t="n">
+      <c r="E29" s="57" t="n">
         <v>3.048</v>
       </c>
       <c r="F29" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="G29" s="55" t="n">
+      <c r="G29" s="57" t="n">
         <v>2.769</v>
       </c>
     </row>
@@ -4953,19 +5094,19 @@
       <c r="B30" s="34" t="n">
         <v>13</v>
       </c>
-      <c r="C30" s="54" t="n">
+      <c r="C30" s="56" t="n">
         <v>2.413</v>
       </c>
       <c r="D30" s="34" t="n">
         <v>14</v>
       </c>
-      <c r="E30" s="54" t="n">
+      <c r="E30" s="56" t="n">
         <v>2.108</v>
       </c>
       <c r="F30" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="G30" s="54" t="n">
+      <c r="G30" s="56" t="n">
         <v>1.829</v>
       </c>
     </row>
@@ -4973,19 +5114,19 @@
       <c r="B31" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="C31" s="55" t="n">
+      <c r="C31" s="57" t="n">
         <v>1.651</v>
       </c>
       <c r="D31" s="36" t="n">
         <v>17</v>
       </c>
-      <c r="E31" s="55" t="n">
+      <c r="E31" s="57" t="n">
         <v>1.473</v>
       </c>
       <c r="F31" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="G31" s="55" t="n">
+      <c r="G31" s="57" t="n">
         <v>1.245</v>
       </c>
     </row>
@@ -4993,19 +5134,19 @@
       <c r="B32" s="34" t="n">
         <v>19</v>
       </c>
-      <c r="C32" s="54" t="n">
+      <c r="C32" s="56" t="n">
         <v>1.067</v>
       </c>
       <c r="D32" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="E32" s="54" t="n">
+      <c r="E32" s="56" t="n">
         <v>0.889</v>
       </c>
       <c r="F32" s="34" t="n">
         <v>22</v>
       </c>
-      <c r="G32" s="54" t="n">
+      <c r="G32" s="56" t="n">
         <v>0.711</v>
       </c>
     </row>
@@ -5044,16 +5185,16 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="18" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
@@ -5061,7 +5202,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="30" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
@@ -5070,7 +5211,7 @@
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="19" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="20"/>
@@ -5079,301 +5220,202 @@
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="23" t="s">
-        <v>273</v>
+        <v>309</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="F5" s="23" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="47" t="n">
-        <v>15.875</v>
-      </c>
-      <c r="C6" s="47" t="n">
-        <v>1.651</v>
-      </c>
-      <c r="D6" s="47" t="n">
-        <v>1.245</v>
-      </c>
-      <c r="E6" s="47" t="n">
-        <v>1.245</v>
-      </c>
-      <c r="F6" s="49" t="s">
-        <v>299</v>
+      <c r="B6" s="33" t="s">
+        <v>312</v>
+      </c>
+      <c r="C6" s="58" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="D6" s="49" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="E6" s="50" t="s">
+        <v>313</v>
+      </c>
+      <c r="F6" s="51" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="51" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="C7" s="51" t="n">
-        <v>2.108</v>
-      </c>
-      <c r="D7" s="51" t="n">
-        <v>1.651</v>
-      </c>
-      <c r="E7" s="51" t="n">
-        <v>1.651</v>
-      </c>
-      <c r="F7" s="53" t="s">
-        <v>300</v>
+      <c r="B7" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="C7" s="59" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D7" s="53" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="E7" s="54" t="s">
+        <v>316</v>
+      </c>
+      <c r="F7" s="55" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="47" t="n">
-        <v>22.225</v>
-      </c>
-      <c r="C8" s="47" t="n">
-        <v>2.108</v>
-      </c>
-      <c r="D8" s="47" t="n">
-        <v>1.651</v>
-      </c>
-      <c r="E8" s="47" t="n">
-        <v>1.651</v>
-      </c>
-      <c r="F8" s="49" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="51" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="C9" s="51" t="n">
-        <v>2.108</v>
-      </c>
-      <c r="D9" s="51" t="n">
-        <v>2.108</v>
-      </c>
-      <c r="E9" s="51" t="n">
-        <v>1.651</v>
-      </c>
-      <c r="F9" s="53" t="s">
-        <v>302</v>
-      </c>
-    </row>
+      <c r="B8" s="33" t="s">
+        <v>318</v>
+      </c>
+      <c r="C8" s="58" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="D8" s="49" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>319</v>
+      </c>
+      <c r="F8" s="51" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="47" t="n">
-        <v>31.75</v>
-      </c>
-      <c r="C10" s="47" t="n">
-        <v>2.769</v>
-      </c>
-      <c r="D10" s="47" t="n">
-        <v>2.108</v>
-      </c>
-      <c r="E10" s="47" t="n">
-        <v>2.108</v>
-      </c>
-      <c r="F10" s="49" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="51" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="C11" s="51" t="n">
-        <v>2.769</v>
-      </c>
-      <c r="D11" s="51" t="n">
-        <v>2.769</v>
-      </c>
-      <c r="E11" s="51" t="n">
-        <v>2.108</v>
-      </c>
-      <c r="F11" s="53" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="47" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="C12" s="47" t="n">
-        <v>2.769</v>
-      </c>
-      <c r="D12" s="47" t="n">
-        <v>2.769</v>
-      </c>
-      <c r="E12" s="47" t="n">
-        <v>2.108</v>
-      </c>
-      <c r="F12" s="49" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="51" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="C13" s="51" t="n">
-        <v>3.404</v>
-      </c>
-      <c r="D13" s="51" t="n">
-        <v>3.048</v>
-      </c>
-      <c r="E13" s="51" t="n">
-        <v>2.769</v>
-      </c>
-      <c r="F13" s="53" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="47" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="C14" s="47" t="n">
-        <v>3.404</v>
-      </c>
-      <c r="D14" s="47" t="n">
-        <v>3.048</v>
-      </c>
-      <c r="E14" s="47" t="n">
-        <v>2.769</v>
-      </c>
-      <c r="F14" s="49" t="s">
-        <v>307</v>
-      </c>
-    </row>
+      <c r="B10" s="37" t="s">
+        <v>321</v>
+      </c>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+    </row>
+    <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="23" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="E16" s="23" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="56" t="s">
-        <v>311</v>
-      </c>
-      <c r="C17" s="57" t="s">
-        <v>312</v>
-      </c>
-      <c r="D17" s="57"/>
-      <c r="E17" s="58" t="s">
-        <v>313</v>
+      <c r="B17" s="60" t="s">
+        <v>325</v>
+      </c>
+      <c r="C17" s="61" t="s">
+        <v>326</v>
+      </c>
+      <c r="D17" s="61"/>
+      <c r="E17" s="62" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="59" t="s">
-        <v>314</v>
-      </c>
-      <c r="C18" s="60" t="s">
-        <v>315</v>
-      </c>
-      <c r="D18" s="60"/>
-      <c r="E18" s="58" t="s">
-        <v>313</v>
+      <c r="B18" s="63" t="s">
+        <v>328</v>
+      </c>
+      <c r="C18" s="64" t="s">
+        <v>329</v>
+      </c>
+      <c r="D18" s="64"/>
+      <c r="E18" s="62" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="56" t="s">
-        <v>316</v>
-      </c>
-      <c r="C19" s="57" t="s">
-        <v>317</v>
-      </c>
-      <c r="D19" s="57"/>
-      <c r="E19" s="58" t="s">
-        <v>313</v>
+      <c r="B19" s="60" t="s">
+        <v>330</v>
+      </c>
+      <c r="C19" s="61" t="s">
+        <v>331</v>
+      </c>
+      <c r="D19" s="61"/>
+      <c r="E19" s="62" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="59" t="s">
-        <v>318</v>
-      </c>
-      <c r="C20" s="60" t="s">
-        <v>319</v>
-      </c>
-      <c r="D20" s="60"/>
-      <c r="E20" s="58" t="s">
-        <v>313</v>
+      <c r="B20" s="63" t="s">
+        <v>332</v>
+      </c>
+      <c r="C20" s="64" t="s">
+        <v>333</v>
+      </c>
+      <c r="D20" s="64"/>
+      <c r="E20" s="62" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="56" t="s">
-        <v>320</v>
-      </c>
-      <c r="C21" s="57" t="s">
-        <v>321</v>
-      </c>
-      <c r="D21" s="57"/>
-      <c r="E21" s="58" t="s">
-        <v>313</v>
+      <c r="B21" s="60" t="s">
+        <v>334</v>
+      </c>
+      <c r="C21" s="61" t="s">
+        <v>335</v>
+      </c>
+      <c r="D21" s="61"/>
+      <c r="E21" s="62" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="59" t="s">
-        <v>322</v>
-      </c>
-      <c r="C22" s="60" t="s">
-        <v>323</v>
-      </c>
-      <c r="D22" s="60"/>
-      <c r="E22" s="58" t="s">
-        <v>313</v>
+      <c r="B22" s="63" t="s">
+        <v>336</v>
+      </c>
+      <c r="C22" s="64" t="s">
+        <v>337</v>
+      </c>
+      <c r="D22" s="64"/>
+      <c r="E22" s="62" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="56" t="s">
-        <v>324</v>
-      </c>
-      <c r="C23" s="57" t="s">
-        <v>325</v>
-      </c>
-      <c r="D23" s="57"/>
-      <c r="E23" s="58" t="s">
-        <v>313</v>
+      <c r="B23" s="60" t="s">
+        <v>338</v>
+      </c>
+      <c r="C23" s="61" t="s">
+        <v>339</v>
+      </c>
+      <c r="D23" s="61"/>
+      <c r="E23" s="62" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="59" t="s">
-        <v>326</v>
-      </c>
-      <c r="C24" s="60" t="s">
+      <c r="B24" s="63" t="s">
+        <v>340</v>
+      </c>
+      <c r="C24" s="64" t="s">
+        <v>341</v>
+      </c>
+      <c r="D24" s="64"/>
+      <c r="E24" s="62" t="s">
         <v>327</v>
       </c>
-      <c r="D24" s="60"/>
-      <c r="E24" s="58" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="56" t="s">
-        <v>328</v>
-      </c>
-      <c r="C25" s="57" t="s">
-        <v>329</v>
-      </c>
-      <c r="D25" s="57"/>
-      <c r="E25" s="58" t="s">
-        <v>313</v>
-      </c>
-    </row>
+    </row>
+    <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="19" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="20"/>
@@ -5395,7 +5437,7 @@
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="21" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="C29" s="38" t="s">
         <v>52</v>
@@ -5410,7 +5452,7 @@
     </row>
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="21" t="s">
-        <v>284</v>
+        <v>343</v>
       </c>
       <c r="C30" s="38" t="s">
         <v>56</v>
@@ -5425,12 +5467,12 @@
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="21" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="C31" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="D31" s="61" t="str">
+      <c r="D31" s="65" t="str">
         <f aca="false">INPUTS!D30</f>
         <v>SA-179 / SMLS CS</v>
       </c>
@@ -5440,14 +5482,14 @@
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="21" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="D32" s="41" t="n">
-        <f aca="false">IFERROR(INDEX(C6:C14,MATCH(D29,B6:B14,0)),"OD not in table")</f>
-        <v>2.108</v>
+        <f aca="false">C6</f>
+        <v>2.11</v>
       </c>
       <c r="E32" s="21" t="s">
         <v>53</v>
@@ -5455,14 +5497,14 @@
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="21" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="C33" s="38" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="D33" s="41" t="n">
-        <f aca="false">IFERROR(INDEX(D6:D14,MATCH(D29,B6:B14,0)),"OD not in table")</f>
-        <v>1.651</v>
+        <f aca="false">C7</f>
+        <v>1.47</v>
       </c>
       <c r="E33" s="21" t="s">
         <v>53</v>
@@ -5470,14 +5512,14 @@
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="21" t="s">
-        <v>287</v>
+        <v>349</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="D34" s="41" t="n">
-        <f aca="false">INPUTS!D14*(1-INPUTS!D39/100)</f>
-        <v>1.84625</v>
+        <f aca="false">C8</f>
+        <v>1.07</v>
       </c>
       <c r="E34" s="21" t="s">
         <v>53</v>
@@ -5485,20 +5527,23 @@
     </row>
     <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="42" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="C35" s="42"/>
       <c r="D35" s="43" t="str">
-        <f aca="false">IF(ISNUMBER(D32),IF(D34&gt;=D32,"PASS","FAIL"),"Check OD")</f>
-        <v>FAIL</v>
-      </c>
-      <c r="E35" s="44"/>
+        <f aca="false">IF(D30&gt;=D32,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+      <c r="E35" s="66" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B10:F10"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
@@ -5507,7 +5552,6 @@
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
     <mergeCell ref="B35:C35"/>
   </mergeCells>
   <conditionalFormatting sqref="D35">
@@ -5546,7 +5590,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="18" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
@@ -5554,7 +5598,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="30" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
@@ -5563,7 +5607,7 @@
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="19" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="20"/>
@@ -5571,178 +5615,123 @@
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="23" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="E5" s="23" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="62" t="s">
-        <v>342</v>
-      </c>
-      <c r="C6" s="60" t="s">
-        <v>343</v>
-      </c>
-      <c r="D6" s="60"/>
-      <c r="E6" s="58" t="s">
-        <v>344</v>
+      <c r="B6" s="67" t="s">
+        <v>357</v>
+      </c>
+      <c r="C6" s="64" t="s">
+        <v>358</v>
+      </c>
+      <c r="D6" s="64"/>
+      <c r="E6" s="62" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="63" t="s">
-        <v>345</v>
-      </c>
-      <c r="C7" s="57" t="s">
-        <v>346</v>
-      </c>
-      <c r="D7" s="57"/>
-      <c r="E7" s="58" t="s">
-        <v>344</v>
+      <c r="B7" s="68" t="s">
+        <v>360</v>
+      </c>
+      <c r="C7" s="61" t="s">
+        <v>361</v>
+      </c>
+      <c r="D7" s="61"/>
+      <c r="E7" s="62" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="62" t="s">
-        <v>347</v>
-      </c>
-      <c r="C8" s="60" t="s">
-        <v>348</v>
-      </c>
-      <c r="D8" s="60"/>
-      <c r="E8" s="58" t="s">
-        <v>344</v>
+      <c r="B8" s="67" t="s">
+        <v>362</v>
+      </c>
+      <c r="C8" s="64" t="s">
+        <v>363</v>
+      </c>
+      <c r="D8" s="64"/>
+      <c r="E8" s="62" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="63" t="s">
-        <v>349</v>
-      </c>
-      <c r="C9" s="57" t="s">
-        <v>350</v>
-      </c>
-      <c r="D9" s="57"/>
-      <c r="E9" s="58" t="s">
-        <v>344</v>
+      <c r="B9" s="68" t="s">
+        <v>364</v>
+      </c>
+      <c r="C9" s="61" t="s">
+        <v>365</v>
+      </c>
+      <c r="D9" s="61"/>
+      <c r="E9" s="62" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="62" t="s">
-        <v>351</v>
-      </c>
-      <c r="C10" s="60" t="s">
-        <v>352</v>
-      </c>
-      <c r="D10" s="60"/>
-      <c r="E10" s="58" t="s">
-        <v>344</v>
+      <c r="B10" s="67" t="s">
+        <v>366</v>
+      </c>
+      <c r="C10" s="64" t="s">
+        <v>337</v>
+      </c>
+      <c r="D10" s="64"/>
+      <c r="E10" s="62" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="63" t="s">
-        <v>353</v>
-      </c>
-      <c r="C11" s="57" t="s">
-        <v>354</v>
-      </c>
-      <c r="D11" s="57"/>
-      <c r="E11" s="58" t="s">
-        <v>344</v>
+      <c r="B11" s="68" t="s">
+        <v>367</v>
+      </c>
+      <c r="C11" s="61" t="s">
+        <v>368</v>
+      </c>
+      <c r="D11" s="61"/>
+      <c r="E11" s="62" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="62" t="s">
-        <v>355</v>
-      </c>
-      <c r="C12" s="60" t="s">
-        <v>356</v>
-      </c>
-      <c r="D12" s="60"/>
-      <c r="E12" s="58" t="s">
-        <v>344</v>
+      <c r="B12" s="67" t="s">
+        <v>369</v>
+      </c>
+      <c r="C12" s="64" t="s">
+        <v>370</v>
+      </c>
+      <c r="D12" s="64"/>
+      <c r="E12" s="62" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="63" t="s">
-        <v>357</v>
-      </c>
-      <c r="C13" s="57" t="s">
-        <v>358</v>
-      </c>
-      <c r="D13" s="57"/>
-      <c r="E13" s="58" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="62" t="s">
+      <c r="B13" s="68" t="s">
+        <v>371</v>
+      </c>
+      <c r="C13" s="61" t="s">
+        <v>372</v>
+      </c>
+      <c r="D13" s="61"/>
+      <c r="E13" s="62" t="s">
         <v>359</v>
       </c>
-      <c r="C14" s="60" t="s">
-        <v>360</v>
-      </c>
-      <c r="D14" s="60"/>
-      <c r="E14" s="58" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="63" t="s">
-        <v>361</v>
-      </c>
-      <c r="C15" s="57" t="s">
-        <v>362</v>
-      </c>
-      <c r="D15" s="57"/>
-      <c r="E15" s="58" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="C16" s="60" t="s">
-        <v>364</v>
-      </c>
-      <c r="D16" s="60"/>
-      <c r="E16" s="58" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="63" t="s">
-        <v>365</v>
-      </c>
-      <c r="C17" s="57" t="s">
-        <v>366</v>
-      </c>
-      <c r="D17" s="57"/>
-      <c r="E17" s="58" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="62" t="s">
-        <v>367</v>
-      </c>
-      <c r="C18" s="60" t="s">
-        <v>368</v>
-      </c>
-      <c r="D18" s="60"/>
-      <c r="E18" s="58" t="s">
-        <v>344</v>
-      </c>
-    </row>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="19" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="20"/>
@@ -5764,7 +5753,7 @@
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="21" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="C22" s="38" t="s">
         <v>52</v>
@@ -5779,7 +5768,7 @@
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="21" t="s">
-        <v>370</v>
+        <v>343</v>
       </c>
       <c r="C23" s="38" t="s">
         <v>56</v>
@@ -5794,14 +5783,14 @@
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="21" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D24" s="41" t="n">
-        <f aca="false">IF(D22&lt;=19.05,1.651,IF(D22&lt;=25.4,2.108,2.769))</f>
-        <v>1.651</v>
+        <f aca="false">API_660!C6</f>
+        <v>2.11</v>
       </c>
       <c r="E24" s="21" t="s">
         <v>53</v>
@@ -5809,14 +5798,13 @@
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="21" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>374</v>
-      </c>
-      <c r="D25" s="41" t="n">
-        <f aca="false">INPUTS!D14*(1-INPUTS!D39/100)</f>
-        <v>1.84625</v>
+        <v>377</v>
+      </c>
+      <c r="D25" s="69" t="n">
+        <v>2.108</v>
       </c>
       <c r="E25" s="21" t="s">
         <v>53</v>
@@ -5824,14 +5812,14 @@
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="21" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D26" s="41" t="n">
-        <f aca="false">D25-INPUTS!D37-INPUTS!D38</f>
-        <v>0.84625</v>
+        <f aca="false">MAX(D24,D25)</f>
+        <v>2.11</v>
       </c>
       <c r="E26" s="21" t="s">
         <v>53</v>
@@ -5839,19 +5827,21 @@
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="42" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C27" s="42"/>
       <c r="D27" s="43" t="str">
-        <f aca="false">IF(D23&gt;=D24,"PASS","FAIL")</f>
+        <f aca="false">IF(D23&gt;=D26,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E27" s="44"/>
+      <c r="E27" s="66" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="10">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C7:D7"/>
@@ -5861,11 +5851,6 @@
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
     <mergeCell ref="B27:C27"/>
   </mergeCells>
   <conditionalFormatting sqref="D27">
@@ -5904,23 +5889,23 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="64" t="s">
-        <v>378</v>
-      </c>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
+      <c r="B1" s="70" t="s">
+        <v>382</v>
+      </c>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="65" t="s">
-        <v>379</v>
-      </c>
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
+      <c r="B3" s="71" t="s">
+        <v>383</v>
+      </c>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="32" t="s">
@@ -5936,7 +5921,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5946,51 +5931,51 @@
       <c r="C5" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="67" t="n">
+      <c r="D5" s="73" t="n">
         <f aca="false">INPUTS!D13</f>
         <v>19.05</v>
       </c>
-      <c r="E5" s="68" t="s">
+      <c r="E5" s="74" t="s">
         <v>53</v>
       </c>
       <c r="F5" s="40" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="21" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="67" t="n">
+      <c r="D6" s="73" t="n">
         <f aca="false">INPUTS!D14</f>
         <v>2.11</v>
       </c>
-      <c r="E6" s="68" t="s">
+      <c r="E6" s="74" t="s">
         <v>53</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="21" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="67" t="n">
+      <c r="D7" s="73" t="n">
         <f aca="false">INPUTS!D22</f>
         <v>40</v>
       </c>
-      <c r="E7" s="68" t="s">
+      <c r="E7" s="74" t="s">
         <v>74</v>
       </c>
       <c r="F7" s="40" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6000,51 +5985,51 @@
       <c r="C8" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="67" t="n">
+      <c r="D8" s="73" t="n">
         <f aca="false">INPUTS!D24</f>
         <v>200</v>
       </c>
-      <c r="E8" s="68" t="s">
+      <c r="E8" s="74" t="s">
         <v>81</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="21" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C9" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="D9" s="67" t="n">
+      <c r="D9" s="73" t="n">
         <f aca="false">INPUTS!D31</f>
-        <v>137.9</v>
-      </c>
-      <c r="E9" s="68" t="s">
+        <v>92.6</v>
+      </c>
+      <c r="E9" s="74" t="s">
         <v>96</v>
       </c>
       <c r="F9" s="40" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="21" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C10" s="38" t="s">
         <v>219</v>
       </c>
-      <c r="D10" s="67" t="n">
+      <c r="D10" s="73" t="n">
         <f aca="false">INPUTS!D37+INPUTS!D38</f>
         <v>1</v>
       </c>
-      <c r="E10" s="68" t="s">
+      <c r="E10" s="74" t="s">
         <v>53</v>
       </c>
       <c r="F10" s="40" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6054,21 +6039,21 @@
       <c r="C11" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="D11" s="67" t="n">
+      <c r="D11" s="73" t="n">
         <f aca="false">INPUTS!D39</f>
         <v>12.5</v>
       </c>
-      <c r="E11" s="68" t="s">
+      <c r="E11" s="74" t="s">
         <v>114</v>
       </c>
       <c r="F11" s="40" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="19" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="20"/>
@@ -6077,33 +6062,33 @@
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="23" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="21" t="s">
-        <v>392</v>
-      </c>
-      <c r="C15" s="69" t="s">
-        <v>393</v>
+        <v>396</v>
+      </c>
+      <c r="C15" s="75" t="s">
+        <v>397</v>
       </c>
       <c r="D15" s="41" t="n">
         <f aca="false">ASME_VIII!D18</f>
-        <v>0.273118279569893</v>
-      </c>
-      <c r="E15" s="70" t="str">
+        <v>0.404458598726115</v>
+      </c>
+      <c r="E15" s="76" t="str">
         <f aca="false">IF(ASME_VIII!D23="PASS","PASS","FAIL")</f>
         <v>PASS</v>
       </c>
@@ -6111,16 +6096,16 @@
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="21" t="s">
-        <v>394</v>
-      </c>
-      <c r="C16" s="69" t="s">
-        <v>395</v>
+        <v>398</v>
+      </c>
+      <c r="C16" s="75" t="s">
+        <v>399</v>
       </c>
       <c r="D16" s="41" t="n">
         <f aca="false">ASME_VIII!D38</f>
-        <v>0.136559139784946</v>
-      </c>
-      <c r="E16" s="70" t="str">
+        <v>0.207516339869281</v>
+      </c>
+      <c r="E16" s="76" t="str">
         <f aca="false">IF(ASME_VIII!D38&lt;=ASME_VIII!D18,"N/A (Circ governs)","Check")</f>
         <v>N/A (Circ governs)</v>
       </c>
@@ -6128,16 +6113,16 @@
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="21" t="s">
-        <v>396</v>
-      </c>
-      <c r="C17" s="69" t="s">
-        <v>397</v>
+        <v>400</v>
+      </c>
+      <c r="C17" s="75" t="s">
+        <v>401</v>
       </c>
       <c r="D17" s="41" t="n">
         <f aca="false">ASME_VIII!D19</f>
-        <v>1.45499231950845</v>
-      </c>
-      <c r="E17" s="70" t="str">
+        <v>1.60509554140127</v>
+      </c>
+      <c r="E17" s="76" t="str">
         <f aca="false">IF(INPUTS!D14&gt;=ASME_VIII!D19,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
@@ -6145,16 +6130,16 @@
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="21" t="s">
-        <v>398</v>
-      </c>
-      <c r="C18" s="69" t="s">
-        <v>399</v>
+        <v>402</v>
+      </c>
+      <c r="C18" s="75" t="s">
+        <v>403</v>
       </c>
       <c r="D18" s="41" t="n">
         <f aca="false">TEMA!D22</f>
         <v>1.651</v>
       </c>
-      <c r="E18" s="70" t="str">
+      <c r="E18" s="76" t="str">
         <f aca="false">TEMA!D24</f>
         <v>PASS</v>
       </c>
@@ -6162,33 +6147,33 @@
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="21" t="s">
-        <v>400</v>
-      </c>
-      <c r="C19" s="69" t="s">
-        <v>401</v>
+        <v>404</v>
+      </c>
+      <c r="C19" s="75" t="s">
+        <v>405</v>
       </c>
       <c r="D19" s="41" t="n">
         <f aca="false">API_660!D32</f>
-        <v>2.108</v>
-      </c>
-      <c r="E19" s="70" t="str">
+        <v>2.11</v>
+      </c>
+      <c r="E19" s="76" t="str">
         <f aca="false">API_660!D35</f>
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="F19" s="44"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="21" t="s">
-        <v>402</v>
-      </c>
-      <c r="C20" s="69" t="s">
-        <v>403</v>
+        <v>406</v>
+      </c>
+      <c r="C20" s="75" t="s">
+        <v>407</v>
       </c>
       <c r="D20" s="41" t="n">
-        <f aca="false">IOGP!D24</f>
-        <v>1.651</v>
-      </c>
-      <c r="E20" s="70" t="str">
+        <f aca="false">IOGP!D26</f>
+        <v>2.11</v>
+      </c>
+      <c r="E20" s="76" t="str">
         <f aca="false">IOGP!D27</f>
         <v>PASS</v>
       </c>
@@ -6196,46 +6181,46 @@
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C21" s="3"/>
-      <c r="D21" s="71" t="n">
+      <c r="D21" s="77" t="n">
         <f aca="false">_xlfn.MAXIFS(D15:D20,D15:D20,"&gt;0")</f>
-        <v>2.108</v>
-      </c>
-      <c r="E21" s="72" t="s">
-        <v>405</v>
+        <v>2.11</v>
+      </c>
+      <c r="E21" s="78" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="3" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C22" s="3"/>
-      <c r="D22" s="73" t="n">
+      <c r="D22" s="79" t="n">
         <f aca="false">INPUTS!D14</f>
         <v>2.11</v>
       </c>
-      <c r="E22" s="72" t="s">
-        <v>407</v>
+      <c r="E22" s="78" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="74" t="s">
-        <v>408</v>
-      </c>
-      <c r="C23" s="74"/>
-      <c r="D23" s="75" t="str">
+      <c r="B23" s="80" t="s">
+        <v>412</v>
+      </c>
+      <c r="C23" s="80"/>
+      <c r="D23" s="81" t="str">
         <f aca="false">IF(INPUTS!D14&gt;=_xlfn.MAXIFS(D15:D20,D15:D20,"&gt;0"),"PASS","FAIL — increase wall")</f>
         <v>PASS</v>
       </c>
-      <c r="E23" s="75"/>
-      <c r="F23" s="75"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="81"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="19" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="20"/>
@@ -6244,11 +6229,11 @@
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="21" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="D26" s="41" t="n">
         <f aca="false">ASME_VIII!D21</f>
-        <v>12.7031921841833</v>
+        <v>8.53020736950961</v>
       </c>
       <c r="E26" s="21" t="s">
         <v>96</v>
@@ -6258,9 +6243,9 @@
       <c r="B27" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="D27" s="76" t="n">
+      <c r="D27" s="82" t="n">
         <f aca="false">ASME_VIII!D22</f>
-        <v>127.031921841833</v>
+        <v>85.3020736950961</v>
       </c>
       <c r="E27" s="21" t="s">
         <v>74</v>
@@ -6268,11 +6253,11 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="21" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="D28" s="41" t="n">
         <f aca="false">ASME_VIII!D32</f>
-        <v>12.2517454068241</v>
+        <v>8.22706036745407</v>
       </c>
       <c r="E28" s="21" t="s">
         <v>96</v>
@@ -6281,7 +6266,7 @@
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="19" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="20"/>
@@ -6295,26 +6280,26 @@
       <c r="C31" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="D31" s="67" t="n">
+      <c r="D31" s="73" t="n">
         <f aca="false">INPUTS!D45</f>
         <v>400</v>
       </c>
-      <c r="E31" s="68" t="s">
+      <c r="E31" s="74" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="21" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>414</v>
-      </c>
-      <c r="D32" s="67" t="str">
+        <v>418</v>
+      </c>
+      <c r="D32" s="73" t="str">
         <f aca="false">_xlfn.CONCAT(TEXT(INPUTS!D13,"0.0"),"×",TEXT(INPUTS!D14,"0.00"))</f>
         <v>19.1×2.11</v>
       </c>
-      <c r="E32" s="68" t="s">
+      <c r="E32" s="74" t="s">
         <v>53</v>
       </c>
     </row>
@@ -6325,63 +6310,63 @@
       <c r="C33" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="D33" s="67" t="n">
+      <c r="D33" s="73" t="n">
         <f aca="false">INPUTS!D47</f>
         <v>25.4</v>
       </c>
-      <c r="E33" s="68" t="s">
+      <c r="E33" s="74" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="21" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>416</v>
-      </c>
-      <c r="D34" s="67" t="n">
+        <v>420</v>
+      </c>
+      <c r="D34" s="73" t="n">
         <f aca="false">INPUTS!D17</f>
         <v>4880</v>
       </c>
-      <c r="E34" s="68" t="s">
+      <c r="E34" s="74" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="21" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C35" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="D35" s="67" t="n">
+      <c r="D35" s="73" t="n">
         <f aca="false">INPUTS!D49</f>
         <v>500</v>
       </c>
-      <c r="E35" s="68" t="s">
+      <c r="E35" s="74" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="21" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>419</v>
-      </c>
-      <c r="D36" s="67" t="n">
+        <v>423</v>
+      </c>
+      <c r="D36" s="73" t="n">
         <f aca="false">INPUTS!D45*PI()*INPUTS!D13/1000*INPUTS!D17/1000</f>
         <v>116.822007779329</v>
       </c>
-      <c r="E36" s="68" t="s">
+      <c r="E36" s="74" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="45" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C38" s="45"/>
       <c r="D38" s="45"/>
